--- a/src/attributions/attributions_saliency_traj_245.xlsx
+++ b/src/attributions/attributions_saliency_traj_245.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1140 +999,5692 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0005902127013541758</v>
+        <v>0.1426405608654022</v>
       </c>
       <c r="B2" t="n">
-        <v>0.007056009490042925</v>
+        <v>0.8233611583709717</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004209848411846906</v>
+        <v>0.07746772468090057</v>
       </c>
       <c r="D2" t="n">
-        <v>0.006821965333074331</v>
+        <v>0.1239055171608925</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001773544820025563</v>
+        <v>1.170833110809326</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001495958305895329</v>
+        <v>0.4217891693115234</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001391116296872497</v>
+        <v>0.3066907227039337</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001684908347669989</v>
+        <v>0.2486493587493896</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000343343970598653</v>
+        <v>0.2344872355461121</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004997242358513176</v>
+        <v>0.2336085140705109</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006173133384436369</v>
+        <v>0.7606949210166931</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003762263513635844</v>
+        <v>0.08151113986968994</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00448606489226222</v>
+        <v>0.3270651698112488</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001989910844713449</v>
+        <v>1.349133610725403</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001558850868605077</v>
+        <v>0.1235358044505119</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00155197037383914</v>
+        <v>0.4574901461601257</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001146181486546993</v>
+        <v>0.09859483689069748</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003941430477425456</v>
+        <v>0.1024808958172798</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007131129968911409</v>
+        <v>0.06430725753307343</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0009002091828733683</v>
+        <v>0.1393961012363434</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0001517312484793365</v>
+        <v>0.1538162529468536</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008268601959571242</v>
+        <v>0.3276419341564178</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0001032215513987467</v>
+        <v>0.2553360760211945</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001230558031238616</v>
+        <v>0.4216651618480682</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0003776044759433717</v>
+        <v>0.02533777244389057</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0008278198074549437</v>
+        <v>0.03789964318275452</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0006085295462980866</v>
+        <v>0.3300948739051819</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0006036736886017025</v>
+        <v>0.1291376203298569</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0004192425403743982</v>
+        <v>0.2175034582614899</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0005155991530045867</v>
+        <v>0.04992778599262238</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.001492432435043156</v>
+        <v>0.02955746650695801</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0001629043981665745</v>
+        <v>0.07286234945058823</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.0007103510433807969</v>
+        <v>0.1747367084026337</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0001660012057982385</v>
+        <v>0.1488981246948242</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0006228015990927815</v>
+        <v>0.2033354192972183</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0005881193210370839</v>
+        <v>0.09578009694814682</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0002105348976328969</v>
+        <v>0.2161083072423935</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.00137718056794256</v>
+        <v>0.1250336170196533</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0001091529557015747</v>
+        <v>0.1934709548950195</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0002880623505916446</v>
+        <v>0.2718297243118286</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0004098166828043759</v>
+        <v>0.2162678092718124</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0004669080080930144</v>
+        <v>0.001306528225541115</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.637955761514604e-05</v>
+        <v>0.009981438517570496</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.22449663549196e-05</v>
+        <v>0.08706257492303848</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0008218265138566494</v>
+        <v>0.1537276953458786</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.001409748918376863</v>
+        <v>0.01056890189647675</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.004200208466500044</v>
+        <v>0.2508053481578827</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0004382171609904617</v>
+        <v>0.01343105360865593</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.004174511879682541</v>
+        <v>0.1007579639554024</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.001519067329354584</v>
+        <v>0.2473979145288467</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0003195934696123004</v>
+        <v>0.03933733329176903</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0004122906248085201</v>
+        <v>0.03604495525360107</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.205705302709248e-05</v>
+        <v>0.1120458096265793</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0005687860539183021</v>
+        <v>0.3900944292545319</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.881921293213964e-05</v>
+        <v>0.2240208983421326</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.001714626676402986</v>
+        <v>0.259256511926651</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.001568825333379209</v>
+        <v>0.02894818037748337</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.001057785237208009</v>
+        <v>0.1294547766447067</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.002038036240264773</v>
+        <v>0.2339897304773331</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0002884310961235315</v>
+        <v>0.2510766386985779</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0008982939179986715</v>
+        <v>0.2115416526794434</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0009573440183885396</v>
+        <v>0.08982435613870621</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.000225823387154378</v>
+        <v>0.001365102827548981</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0007163718109950423</v>
+        <v>0.2723382413387299</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.12330705835484e-05</v>
+        <v>0.1250356137752533</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0007263034931384027</v>
+        <v>0.1324638426303864</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0001170952018583193</v>
+        <v>0.009058341383934021</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0002275115548400208</v>
+        <v>0.245226263999939</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0006326035363599658</v>
+        <v>0.05452022701501846</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0004631099000107497</v>
+        <v>0.2959877848625183</v>
       </c>
       <c r="BS2" t="n">
-        <v>3.24439606629312e-05</v>
+        <v>0.03135793283581734</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.0001272372901439667</v>
+        <v>0.1511361300945282</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.001689367927610874</v>
+        <v>0.03580880165100098</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.002148294122889638</v>
+        <v>0.1606746166944504</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.000453491578809917</v>
+        <v>0.1209841147065163</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.001455530524253845</v>
+        <v>0.2446083128452301</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0002324577362742275</v>
+        <v>0.1760253757238388</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0007374808774329722</v>
+        <v>0.2395221889019012</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0002232496917713434</v>
+        <v>0.03106041438877583</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.0004205510776955634</v>
+        <v>0.09198947250843048</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.0008239059243351221</v>
+        <v>0.377451479434967</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0002438765368424356</v>
+        <v>0.07896712422370911</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0009153722203336656</v>
+        <v>0.1905301362276077</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.000611159426625818</v>
+        <v>0.03648737818002701</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.001364771160297096</v>
+        <v>0.08436945825815201</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0001970587618416175</v>
+        <v>0.126316711306572</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0005649673985317349</v>
+        <v>0.1024636700749397</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.0001891103165689856</v>
+        <v>0.06775126606225967</v>
       </c>
       <c r="CK2" t="n">
-        <v>3.391179052414373e-05</v>
+        <v>0.03269318863749504</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0006287976284511387</v>
+        <v>0.05417680740356445</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.001469209091737866</v>
+        <v>0.1344420611858368</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.667657488724217e-05</v>
+        <v>0.1316835284233093</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0004062755906488746</v>
+        <v>0.1123289316892624</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0007577707874588668</v>
+        <v>0.09773218631744385</v>
       </c>
       <c r="CQ2" t="n">
-        <v>7.293654925888404e-05</v>
+        <v>0.5877286791801453</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.00121976260561496</v>
+        <v>0.2316484749317169</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.001481792307458818</v>
+        <v>0.3694218099117279</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.001232164911925793</v>
+        <v>0.02903047017753124</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.0003390930942259729</v>
+        <v>0.2733093500137329</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.000284941925201565</v>
+        <v>0.08985346555709839</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0009321712423115969</v>
+        <v>0.1519397646188736</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.0008255620487034321</v>
+        <v>0.02762026898562908</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.00148151267785579</v>
+        <v>0.09421419352293015</v>
       </c>
       <c r="CZ2" t="n">
-        <v>8.850375161273405e-05</v>
+        <v>0.1742615848779678</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0005582187441177666</v>
+        <v>0.1330918222665787</v>
       </c>
       <c r="DB2" t="n">
-        <v>8.748178515816107e-05</v>
+        <v>0.09889970719814301</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0002061760751530528</v>
+        <v>0.05065740272402763</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0004846308729611337</v>
+        <v>0.04551495239138603</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.0001648763718549162</v>
+        <v>0.2199676781892776</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.001924591138958931</v>
+        <v>0.2338908910751343</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0004704227903857827</v>
+        <v>0.02155778557062149</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.003543657483533025</v>
+        <v>0.1409329175949097</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.003099553287029266</v>
+        <v>0.0376591831445694</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0001520778168924153</v>
+        <v>0.3110508024692535</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.002098645316436887</v>
+        <v>0.03060070425271988</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.001173100201413035</v>
+        <v>0.05171495676040649</v>
       </c>
       <c r="DM2" t="n">
-        <v>7.437908789142966e-05</v>
+        <v>0.004832380451261997</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.0004893625155091286</v>
+        <v>0.007837086915969849</v>
       </c>
       <c r="DO2" t="n">
-        <v>9.057021088665351e-05</v>
+        <v>0.2380593419075012</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.00074307358590886</v>
+        <v>0.1013183295726776</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.932510349433869e-05</v>
+        <v>0.1864022314548492</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0003992532438132912</v>
+        <v>0.3471086621284485</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.0004668673500418663</v>
+        <v>0.1696035414934158</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0002995718095917255</v>
+        <v>0.0733451321721077</v>
       </c>
       <c r="DU2" t="n">
-        <v>9.610124106984586e-05</v>
+        <v>0.2123183906078339</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0007420629845000803</v>
+        <v>0.1540225148200989</v>
       </c>
       <c r="DW2" t="n">
-        <v>6.408528133761138e-05</v>
+        <v>0.1029118746519089</v>
       </c>
       <c r="DX2" t="n">
-        <v>4.148157131567132e-06</v>
+        <v>0.1092418059706688</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0008132694056257606</v>
+        <v>0.05764942616224289</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0007843372877687216</v>
+        <v>0.09736044704914093</v>
       </c>
       <c r="EA2" t="n">
-        <v>1.408892057952471e-05</v>
+        <v>0.09257423132658005</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.000184769116458483</v>
+        <v>0.296215146780014</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.0009841325227171183</v>
+        <v>0.02258696965873241</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0003861980221699923</v>
+        <v>0.04776747897267342</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0004151583416387439</v>
+        <v>0.2352869808673859</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.0004162710683885962</v>
+        <v>0.1306852847337723</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.001095375628210604</v>
+        <v>0.1980544328689575</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.00103950232733041</v>
+        <v>0.1235330700874329</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.001285700825974345</v>
+        <v>0.3010964095592499</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0003115487925242633</v>
+        <v>0.242429718375206</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0006853379891254008</v>
+        <v>0.1187460198998451</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.0001778493460733443</v>
+        <v>0.03495834022760391</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.0004365531785879284</v>
+        <v>0.003042097669094801</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.000396669638575986</v>
+        <v>0.006865183357149363</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0005776003235951066</v>
+        <v>0.009623607620596886</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0008476742659695446</v>
+        <v>0.07490931451320648</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.001155403908342123</v>
+        <v>0.06056943163275719</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.001139285159297287</v>
+        <v>0.1515759527683258</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0005409209406934679</v>
+        <v>0.02004942111670971</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.001817642711102962</v>
+        <v>0.1173452585935593</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.0003672322200145572</v>
+        <v>0.06950397789478302</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0005174655234441161</v>
+        <v>0.1270028650760651</v>
       </c>
       <c r="EW2" t="n">
-        <v>3.939430462196469e-05</v>
+        <v>0.07802781462669373</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.0001552883186377585</v>
+        <v>0.09418885409832001</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.0009844393935054541</v>
+        <v>0.2357324212789536</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0006660202634520829</v>
+        <v>0.01235190406441689</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.001519395038485527</v>
+        <v>0.07903651893138885</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0002995647664647549</v>
+        <v>0.1692143082618713</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.0004884210065938532</v>
+        <v>0.153629794716835</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.0002335721219424158</v>
+        <v>0.09197013080120087</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.0002304620866198093</v>
+        <v>0.1217319667339325</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0005558182019740343</v>
+        <v>0.07666100561618805</v>
       </c>
       <c r="FG2" t="n">
-        <v>9.914708789438009e-05</v>
+        <v>0.0278354212641716</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.0006748571177013218</v>
+        <v>0.1503224968910217</v>
       </c>
       <c r="FI2" t="n">
-        <v>8.199006515496876e-06</v>
+        <v>0.1431671977043152</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0009234974277205765</v>
+        <v>0.1392288953065872</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.0003760894178412855</v>
+        <v>0.2382644563913345</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0004973522736690938</v>
+        <v>0.1575699895620346</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.0005614063120447099</v>
+        <v>0.007278598845005035</v>
       </c>
       <c r="FN2" t="n">
-        <v>8.964005974121392e-05</v>
+        <v>0.2894421517848969</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0001693135563982651</v>
+        <v>0.4537738561630249</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0001679098058957607</v>
+        <v>0.03661347553133965</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0014880639500916</v>
+        <v>0.04630409181118011</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.001545571489259601</v>
+        <v>0.2637324929237366</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0003811880596913397</v>
+        <v>0.1932639479637146</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.0008089217590168118</v>
+        <v>0.4314495325088501</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0005751490243710577</v>
+        <v>0.3708696365356445</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.000205638338229619</v>
+        <v>0.3128671944141388</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.0004247219476383179</v>
+        <v>0.2726184725761414</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.0005102311260998249</v>
+        <v>0.107627660036087</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.0002335192257305607</v>
+        <v>0.02438577637076378</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.0004094079486094415</v>
+        <v>9.644031524658203e-05</v>
       </c>
       <c r="GA2" t="n">
-        <v>9.55013238126412e-05</v>
+        <v>0.05109366029500961</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0006778824026696384</v>
+        <v>0.110568456351757</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.0006130545516498387</v>
+        <v>0.1454310864210129</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.0002492291096132249</v>
+        <v>0.1910925209522247</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.002722714561969042</v>
+        <v>0.04835762828588486</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.0005604800535365939</v>
+        <v>0.3648818731307983</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.000466621684608981</v>
+        <v>0.2080216854810715</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.008563951589167118</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.06261146068572998</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0299411341547966</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.004784907214343548</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.01224867720156908</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.03953996300697327</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.02866366133093834</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.003795165568590164</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.003284514881670475</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.0163834486156702</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.06972314417362213</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.03286579251289368</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.005751519463956356</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.03606824576854706</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.03400978073477745</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.02586938254535198</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.008363007567822933</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.001784263295121491</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.00667043961584568</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.01570448838174343</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.003746253438293934</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.0003841054276563227</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.005877682007849216</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.01908100582659245</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.006910266354680061</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.0006687529967166483</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.001304422970861197</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.01113233622163534</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.01521783042699099</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.00312235695309937</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.02232781611382961</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.01271190587431192</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.01565276086330414</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.009822871536016464</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>7.783540058881044e-05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.001051590545102954</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.004218772053718567</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.01559476740658283</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.002747780410572886</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.000894713681191206</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.02722826227545738</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.01265939231961966</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.004478590562939644</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.003352258121594787</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.006010906305164099</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.001775233075022697</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.04105633124709129</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.01050394307821989</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.009924422018229961</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.008442253805696964</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.02182257175445557</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.003979997709393501</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.008377798832952976</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.00813471432775259</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.02196830883622169</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.01500950381159782</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.01684469170868397</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.006782117299735546</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.02227605879306793</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.007985341362655163</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.02929003350436687</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.0319853350520134</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.002437744056805968</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.009457014501094818</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.009227806702256203</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.01088198460638523</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.01670766063034534</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.003080770839005709</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.007858287543058395</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.01802631095051765</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.006401034072041512</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.005216229241341352</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.008203610777854919</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.04967730119824409</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.008146772161126137</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.001277842675335705</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.006801010109484196</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.02679265663027763</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.004695832263678312</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.001721473876386881</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.001718973857350647</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.001391288940794766</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.02190933562815189</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.0126199834048748</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.0006207828409969807</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.0002307163522345945</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.002677863696590066</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.001690319972112775</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>0.004260563291609287</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.0009352549095638096</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.02009806782007217</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.01652319170534611</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.0167801808565855</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.03463798761367798</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.0008939506369642913</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.004773312713950872</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.004778755828738213</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.01385112758725882</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.005176528356969357</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.005826930515468121</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.02311170101165771</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.01255736500024796</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.001735458732582629</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.005991577636450529</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.004952507559210062</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.004319974221289158</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.003361172042787075</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.0007616509101353586</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.01340377330780029</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.01925937086343765</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.0005081028211861849</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.008738888427615166</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.001766213565133512</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.02073101699352264</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.009087726473808289</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.00927308201789856</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.01049247663468122</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.003506824839860201</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.01521803624927998</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.005252901464700699</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.002532017882913351</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.004775385838001966</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.005776515230536461</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.0009134816937148571</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.003828063607215881</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.0108806723728776</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.008295169100165367</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.001597892958670855</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.01495223492383957</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.006513966713100672</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.006135236471891403</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.008747591637074947</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.0004509394057095051</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.005727071780711412</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.01390378456562757</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.005309391301125288</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.02228531613945961</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.003481691237539053</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.005008645355701447</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>0.004489590879529715</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.01121811196208</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.001416347455233335</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.001388077042065561</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.002060668775811791</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.003248421475291252</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.01488086208701134</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.009867527522146702</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.0008908875752240419</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.009950346313416958</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.0008153789094649255</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.01183419395238161</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.0005367974517866969</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.008002998307347298</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.0006891124648973346</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.02588882483541965</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>0.009501997381448746</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.002834020415320992</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.0003719886590261012</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.005198347382247448</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.002046633511781693</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.001719849766232073</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.001053922111168504</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.004384075291454792</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.01552954874932766</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.00644992757588625</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.008512150496244431</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.01516452990472317</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.008557919412851334</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.002723756479099393</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.002281921217218041</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.007854197174310684</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.005236944183707237</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.02735726535320282</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.02708167769014835</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.02268572151660919</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.01932521350681782</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.01291495654731989</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.01038087904453278</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.01492662914097309</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.01621321216225624</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.005587760359048843</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.02849609777331352</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.03078413568437099</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.001955956453457475</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.002382193226367235</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.01783984899520874</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.002912977943196893</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.008931495249271393</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>0.003186233341693878</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5.254971124912799e-09</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.948681476766524e-08</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.10607354386616e-08</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.159300389019791e-08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.986715289121094e-09</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.090994127319391e-08</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.857348632318462e-09</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.790759954355963e-09</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.430993279427639e-08</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.338942373114605e-10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.634021439324897e-08</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.005875288091374e-08</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.048709729114307e-08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.594445464547789e-08</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.229938710409442e-08</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.75469305752074e-09</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.422261502488254e-09</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.268235294560327e-08</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8.904931236841662e-10</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9.198300787716107e-09</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.618774530560586e-09</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.216461040902232e-09</v>
+      </c>
+      <c r="W4" t="n">
+        <v>9.524830701934661e-09</v>
+      </c>
+      <c r="X4" t="n">
+        <v>9.558808855558709e-09</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.065517629683654e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.315478889324822e-09</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>7.111945699023181e-09</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.225815804417607e-08</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.366492557470679e-09</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.215694656053756e-09</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.381763858887552e-08</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.306287700231223e-08</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.785784853325367e-08</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>4.134697917379526e-09</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>3.233087042531224e-08</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.77334252732453e-09</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>9.761523811491202e-10</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>8.297135423163127e-09</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7.996829864964639e-10</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.643403413353894e-09</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4.524686403328815e-09</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.199928405057562e-09</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.515011806764505e-09</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9.372582709943345e-09</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.531913567693778e-09</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.444261124727291e-09</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.30956035302188e-08</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>6.01814509337828e-09</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3.241227286565618e-09</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.422826916870235e-08</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.145759208678101e-08</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>9.082528507065035e-09</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.209487621167682e-09</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.101913614855789e-09</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7.688473857569988e-09</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9.362567610082806e-09</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.267456006814882e-08</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.584727193915114e-08</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>8.446086496860516e-09</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1.188578124811102e-10</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.092234024393292e-09</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.315665887346995e-08</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.840593277790958e-08</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>9.74474945181214e-11</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.117686299068055e-08</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.743151401001342e-09</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2.930201192796744e-09</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>7.261733436791928e-09</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>2.847515778725551e-09</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1.141322236719589e-08</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>5.088790278051647e-09</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1.263210869240083e-08</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>2.510006646971874e-09</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>2.358460982065935e-08</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>5.837708094702521e-11</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1.504745217317804e-09</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>6.330366453255465e-09</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>2.267048770931979e-08</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>6.287367515511733e-09</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>2.721298741903411e-09</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>2.21829221658254e-09</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>2.728893111481057e-09</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>1.036500751894209e-08</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>2.010781763317482e-09</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2.68484035004235e-09</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>2.7335342878132e-09</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>7.894500164695728e-09</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>2.579575719696692e-10</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>3.804104586890844e-09</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>4.574208567476035e-09</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>3.726551955907098e-09</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>1.274741823209524e-08</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1.136419403025002e-08</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1.854544606771924e-08</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>3.561311912037013e-09</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>1.420573703114769e-08</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>4.665166919437524e-09</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>1.525020820736245e-08</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1.422999162947747e-09</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>3.271984905239833e-09</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>9.707968651184729e-09</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>2.934281262412242e-09</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>6.075046243836368e-09</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>4.047051138655888e-09</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.022266893357937e-08</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>1.170559649210645e-09</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>4.240918727305143e-09</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>3.965982209308549e-09</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>4.662025876456255e-09</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>4.37835545596954e-09</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>7.892300146750131e-10</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>3.720672214768683e-09</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>1.055793674709093e-09</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>8.605115731086244e-09</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>2.089186823539535e-09</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>1.581596364985671e-08</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>3.061249476132843e-09</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>4.642330964088615e-09</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>8.777821802752328e-10</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>2.678524513299863e-09</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>5.835619543148596e-09</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>6.978809086177762e-09</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>2.921008768197453e-09</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>6.495318061183752e-09</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>1.368071078644562e-08</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>5.18601783738859e-09</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>1.932061843845645e-09</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>6.817629571997941e-09</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>9.232692832483735e-09</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>9.007696810670041e-09</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>5.524311230686862e-09</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>3.079603239086737e-10</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>3.190169461930736e-09</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>1.19798411191141e-08</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>7.846233884833964e-09</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>1.564239626716812e-09</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>2.850331082271396e-09</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>4.211154980282572e-09</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>2.074675986563079e-09</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>1.902062285452644e-09</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>8.472029744410747e-10</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>8.105748017239733e-11</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>3.576677842787035e-11</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>1.577598718327522e-09</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>3.240458346098762e-09</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>5.768656219373725e-09</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>1.117106962489345e-09</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>2.002890298058446e-09</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>4.234497197330711e-10</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>1.131174975910199e-08</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>5.802959890388593e-09</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>4.784533658153123e-09</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>1.271071359276732e-09</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>2.889724903809565e-09</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>1.177180752875984e-08</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>9.3012247903701e-10</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>6.389665685446744e-09</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>1.53741130937135e-09</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>7.159668857781298e-09</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>1.025813808896991e-10</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>1.117774761638657e-09</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>9.400100697831704e-10</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>2.167943824460394e-09</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>9.834749015169564e-09</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>6.430386889633155e-09</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>6.542599795267279e-09</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>4.310201084933851e-09</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>1.735846133499308e-08</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>2.240072127790427e-09</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>5.626816790282874e-09</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>1.946755112669507e-08</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>2.567550616561221e-10</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>1.736759713821812e-08</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>1.573149077671587e-08</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>2.497740014817396e-09</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>2.64564938845524e-08</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>3.36000627321198e-09</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>4.173553946884567e-09</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>1.098109070341025e-08</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>1.039083930010065e-09</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>1.524604664737694e-09</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>9.8770402967574e-10</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>9.567225234263788e-09</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>5.071784769938859e-09</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>1.948775540938641e-08</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>1.665457993738073e-08</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>3.950614058112478e-09</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>1.223109169501413e-09</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>1.918811332046744e-09</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6.268781937990298e-09</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.247173114255929e-08</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8.622447200679062e-10</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.251645062211765e-09</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.990438119354621e-09</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.926008152963732e-08</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.581481777814588e-10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.972189048326527e-09</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.929645053801778e-09</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.227574177510633e-10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.656967623693163e-08</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.61693083764203e-09</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.465307253312176e-08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.184990061631197e-08</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.099960916268628e-08</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.901562018957748e-09</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.443082098262494e-09</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.104207640409641e-09</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.373783474813763e-09</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8.712675025890348e-11</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.858123515636635e-09</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.397660902100142e-09</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.201760551656662e-09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.310920566017671e-09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.939568144455507e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.321386638470813e-09</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.87794851786083e-10</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.775060678090085e-10</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.568757093816657e-09</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>8.435152576424798e-10</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.365926648513096e-09</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7.611760111103649e-09</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.672234568824933e-09</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.274270355899887e-09</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.368639335197486e-08</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.020322715206134e-09</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>4.819664223276732e-09</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.866821529641129e-09</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>6.786379014300792e-09</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2.700789814014115e-09</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2.293456535795713e-09</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.74540923328459e-09</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.426951528633481e-09</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.725176113076543e-09</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3.22427951005011e-09</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.041169342552166e-09</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.943920402425192e-08</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7.881230779105408e-09</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2.01072936079072e-09</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2.075187310879301e-08</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.811489092062857e-08</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>3.0854581112294e-09</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.185577135411677e-09</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>2.129343590340227e-09</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.994663545445974e-09</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.413486160397383e-09</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.112809482923694e-09</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>7.513299316030952e-09</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6.551040598878899e-09</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.414890731827768e-09</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>5.153936832869022e-09</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.033189445109883e-08</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7.532149348676853e-10</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1.445539243860594e-10</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>6.452186340766275e-09</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.736119026318761e-09</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.227054458041721e-09</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>7.604938900840352e-09</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>6.916918149357798e-10</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>5.9149827258409e-09</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>4.212158621896833e-09</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>3.096895406784483e-09</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>3.390156155802515e-09</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>6.060538293439777e-09</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>3.967266959392646e-09</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1.619273604092086e-10</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>2.859395831222855e-09</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>8.983935373407803e-09</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>5.264603419874447e-09</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>2.330947435069675e-09</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>3.498328293716213e-10</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>2.359346606972679e-10</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>7.216682806898689e-09</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.112464647652246e-10</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.058283987693699e-09</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>2.455199821227438e-09</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>4.856852697798786e-09</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.60694124673455e-10</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>2.501244544816927e-09</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>2.088857753435036e-09</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>4.522370034010237e-09</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>7.874750629355276e-09</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.254867143529736e-08</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>8.076048274574532e-09</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>4.299615774527865e-09</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>2.670258902881528e-09</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>1.160160967295099e-09</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>6.65402133392945e-09</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>4.955504895320928e-09</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1.452197362361574e-09</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>6.720001444193713e-09</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>6.344190728313492e-10</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>3.277670579393543e-09</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>2.727856385220662e-09</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>5.831317206883568e-09</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>9.761154107224002e-10</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.959943318752266e-09</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>1.282444705985597e-09</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>2.676230903553289e-10</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.381493586194438e-09</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>1.785675385335139e-09</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>2.408517829621815e-09</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>1.837290097839173e-09</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>9.004509138321737e-09</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>2.262788845186492e-09</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>5.745679487745292e-09</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>2.946589194863236e-09</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>2.142732435927996e-09</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>2.344060501258127e-09</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>1.609239963507036e-09</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>4.47778480960892e-10</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>1.304033325766341e-09</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>3.886658772600526e-10</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>2.413466981820989e-09</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>6.187852896744062e-09</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>4.840981837617164e-09</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>2.743840932240005e-09</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>3.347888188898196e-09</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>5.63180257984186e-09</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>3.063913345258129e-09</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>7.313501471095663e-10</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>3.915870294690649e-09</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>1.85792714546551e-10</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>9.520403132512456e-09</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>4.576754530916105e-09</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>2.566859613750694e-09</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>1.579193553702396e-09</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>2.530342158024723e-09</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>6.883825176551284e-10</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>1.664984816684978e-09</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>3.467715448124409e-09</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>2.14759454664204e-09</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>4.539189857322157e-10</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>1.385310199886192e-10</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>1.029383911443915e-09</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>3.386975588881569e-09</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>6.824274478844927e-11</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>5.685035775471192e-10</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>9.155979308062001e-10</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>7.291486303628858e-10</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>4.031292522022056e-10</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>1.743171829104995e-09</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>2.085107642102457e-09</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>3.829335182281568e-10</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>7.832291260001512e-09</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>3.373784862592544e-10</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>3.702685935635941e-09</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>1.071377320194244e-09</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>3.716221108618356e-09</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>2.106026741888201e-10</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>2.548569133509204e-09</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>5.067250508083987e-10</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>4.827577226862445e-11</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>5.579868123106735e-09</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>4.598130765032238e-09</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>4.599113090364426e-09</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>3.094717371254774e-09</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>5.594599450375881e-09</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>2.477401617184682e-09</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>3.228688427725501e-09</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>1.126156501385367e-08</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>6.00923044657975e-09</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>1.099728041964454e-08</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>8.294386510954155e-09</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>2.180354341518864e-09</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>1.341037836333214e-09</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>4.363381878036421e-10</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>4.779711293423361e-09</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>1.031825291875066e-08</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>2.473848459416672e-09</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>1.697315399340482e-09</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>2.048571756674278e-09</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>7.180507743953513e-09</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>1.305109131877202e-09</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>1.246911640606641e-08</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>9.527722610869205e-09</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>2.544945809646038e-09</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>1.526915927030359e-09</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>2.939986032401976e-09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2.361168299103156e-05</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.0005069130565971136</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0001795350108295679</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0002098018449032679</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.854811853263527e-05</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0005148540949448943</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.986057319911197e-05</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0002314954035682604</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0001216529490193352</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0001035200548358262</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0005949715850874782</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0002499231486581266</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0004454495501704514</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0002209945232607424</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0006037885323166847</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.679514313465916e-05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.011048728600144e-05</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0001259000127902254</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0001028400292852893</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.836438165511936e-05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6.479662260971963e-06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.498981797951274e-05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>9.0493616880849e-05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.0001262586301891133</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.000115302660560701</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0001290798682020977</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.350792293436825e-05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.624336674576625e-05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.709173713810742e-05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>9.595199662726372e-05</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0001256077375728637</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0001428814139217138</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0002142470475519076</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3.422261215746403e-05</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0003720480599440634</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.369873436691705e-05</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>9.070755913853645e-05</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6.020470027578995e-05</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5.082981078885496e-05</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>8.072535274550319e-05</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.0001110259108827449</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8.928793977247551e-05</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.505390693841036e-05</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8.149011409841478e-05</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.865069735795259e-06</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.0001192790296045132</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.0004193305503576994</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.000161472344188951</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.0001261488650925457</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.0004223840369377285</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.0004671081260312349</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.783812695066445e-05</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.002384856808931e-05</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.033380976878107e-05</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.0001262123550986871</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.683610728126951e-05</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.0001276154507650062</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.0001322798780165613</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.0002016730722971261</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>6.226840196177363e-05</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>4.01230608986225e-05</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.0002573454694356769</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6.507713987957686e-05</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>2.632092946441844e-05</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.0001428815448889509</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.200373561820015e-05</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>9.874247189145535e-05</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.0001209231413668022</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7.09518208168447e-05</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>9.490567026659846e-05</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>8.161296136677265e-05</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>8.107542817015201e-05</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>7.68398167565465e-05</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.0001625911827431992</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>3.023509634658694e-06</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>4.858869942836463e-06</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>3.40317128575407e-05</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.000246440147748217</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.000181739596882835</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>5.946312376181595e-05</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>9.500309533905238e-05</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1.288792736886535e-05</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.0001655761443544179</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>5.597477138508111e-05</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>4.660504782805219e-05</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>4.7318622819148e-05</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.0001290224900003523</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>9.572506314725615e-06</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>2.894245517381933e-05</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>5.926540325162932e-07</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>6.446013867389411e-05</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>5.944474833086133e-05</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.0001833692804211751</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.000131472508655861</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>8.936096855904907e-05</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>5.406925993156619e-05</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.0001602765842108056</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.000236167325056158</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.0001049040656653233</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>5.488972965395078e-05</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.000141042226459831</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>7.862330676289275e-05</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>7.207577436929569e-05</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>5.295799928717315e-05</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.0001679480192251503</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>2.975814277306199e-05</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>3.088625817326829e-05</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>9.534956916468218e-06</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>1.014861663861666e-05</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.0001996315259020776</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.0001691967772785574</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.0001031243882607669</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>2.946358472399879e-05</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.0001469608250772581</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>1.592321677890141e-05</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.0002006993163377047</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>4.118921788176522e-05</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>5.153475649422035e-05</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.0001198892714455724</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>3.115959771093912e-05</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.0001183942731586285</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>6.550193575094454e-06</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>9.324280836153775e-05</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.000108953652670607</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.0002086389577016234</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>8.024144335649908e-05</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>9.370094630867243e-06</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>5.969551421003416e-05</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.000173809879925102</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>3.559144715836737e-06</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.0001500970683991909</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>2.175756162614562e-05</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.0001604059507371858</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.0001592575281392783</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.0001985089620575309</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>1.529207656858489e-05</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>1.874964073067531e-05</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>2.974247763631865e-05</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>5.237366349319927e-05</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>4.416456795297563e-05</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>4.906339017907158e-05</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>3.75697563868016e-05</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>2.771158688119613e-05</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.0001035262685036287</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>5.508178946911357e-05</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.0001177641388494521</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>7.061517680995166e-05</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.0001281744334846735</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>6.693473551422358e-05</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.0001364735799143091</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>2.924345608334988e-06</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>3.99424388888292e-05</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>2.414841765130404e-05</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>4.036410973640159e-05</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.000181354145752266</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>4.441983764991164e-05</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>9.121783659793437e-05</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>4.217864261590876e-05</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.0001293058594455943</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>1.555617927806452e-05</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>2.631771531014238e-05</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>3.487666617729701e-05</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>9.244085958926007e-06</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>7.253210060298443e-05</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.0001024126977426931</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.0001129777883761562</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>1.84786222234834e-05</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.0001790795067790896</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>4.13148918596562e-05</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.000123851903481409</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.0002751050051301718</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.0001100521330954507</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.0001060959839378484</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>1.917616464197636e-05</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>7.538063800893724e-05</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>4.125521081732586e-05</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>5.533142029889859e-05</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.0001398139720549807</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.0004502097144722939</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>9.299379598814994e-06</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>6.750159082002938e-05</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>9.309287997893989e-05</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.0002356324694119394</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>4.595626523951069e-05</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.0002855887578334659</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.0001653600193094462</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>5.797818448627368e-05</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>5.293959839036688e-05</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>1.0623922207742e-05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7.691685459576547e-05</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0003072718100156635</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.086328307399526e-06</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.000139282681629993</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.964583836728707e-05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0002460949181113392</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.335331611102447e-05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.382629024097696e-05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.620859049784485e-05</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.06481044087559e-05</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0003722988767549396</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.619294875534251e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002394993061898276</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0001041201467160136</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0003065447090193629</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.62144388013985e-05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.395979678723961e-05</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.801376391900703e-05</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.669899913598783e-05</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.404895687708631e-05</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.690987796289846e-05</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.376134191057645e-05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.433596480637789e-05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.896780956187285e-05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.684147304738872e-05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.0001411184493917972</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.815244655124843e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.378634134307504e-05</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.182239743182436e-05</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.891817348427139e-05</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>7.368098886217922e-05</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>7.501863001380116e-05</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>9.57558659138158e-05</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.038577920553507e-05</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0002094470110023394</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>3.103895505773835e-05</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>7.265630119945854e-05</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>3.806336462730542e-05</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3.82097132387571e-05</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3.109603494522162e-05</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3.698737600643653e-06</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.573251771944342e-06</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3.918401489499956e-05</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.000139212075737305</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.128598316630814e-05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.0001164827408501878</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.0002425203565508127</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6.464351463364437e-05</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.902298628119752e-05</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.0001876322639873251</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.0001726334303384647</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.942084499110933e-06</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.392642484977841e-06</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.703050944954157e-05</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.221837555931415e-05</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.933384090894833e-05</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.650933700148016e-05</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.0001169502138509415</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>7.435803854605183e-05</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>5.427400537882932e-05</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.736876922426745e-05</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>8.326924580615014e-05</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.294046422932297e-05</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.321857234870549e-05</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>3.645935066742823e-05</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.886590212052397e-06</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>6.962921179365367e-05</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>2.317588041478302e-05</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.05286089819856e-05</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.000124360216432251</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.833459464251064e-05</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>8.065887232078239e-05</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.784135333262384e-05</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.0001345257624052465</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>2.049492104561068e-05</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>6.383928848663345e-05</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>3.248325811000541e-06</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>8.927455201046541e-05</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>3.400472633074969e-05</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>2.527182368794456e-05</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>4.524458199739456e-05</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1.066539516614284e-05</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>9.209743438987061e-05</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>3.784714863286354e-06</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>3.520170139381662e-05</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.502861596236471e-05</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>8.074149081949145e-05</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2.530566962377634e-05</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.880705167423002e-05</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>3.772290074266493e-05</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>3.250980807933956e-05</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>9.80980257736519e-05</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>8.703589264769107e-05</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.0001225228043040261</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>2.261467670905404e-06</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>8.500288822688162e-05</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>5.848703949595802e-06</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.0001025323872454464</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>3.769935574382544e-05</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>2.348103953409009e-05</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>8.889888704288751e-05</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.058936959452694e-06</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>5.380349466577172e-05</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>1.63135991897434e-05</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>8.741121564526111e-05</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>5.449879608931951e-06</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>2.382257298449986e-05</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>3.269608714617789e-05</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>2.506393684598152e-05</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>5.012480323784985e-05</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>4.254374653100967e-05</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>1.193059233628446e-05</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.0001924586395034567</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>8.084376895567402e-05</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>5.913638233323582e-05</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>1.742140739224851e-06</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>2.927568857558072e-06</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>3.202759035048075e-05</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>6.178076728247106e-05</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>1.819178214645945e-05</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>5.311001586960629e-05</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>2.330850657017436e-05</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>2.551390934968367e-05</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>5.983177834423259e-05</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.0001228998880833387</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>4.802750481758267e-05</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>3.133450445602648e-05</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>1.87354235094972e-05</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>3.274233677075244e-05</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>4.372009425424039e-05</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>6.830459460616112e-05</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>4.313945100875571e-05</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>3.700749584822915e-05</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>6.078441219870001e-05</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>7.395865395665169e-05</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>2.134999022018746e-06</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>2.157592825824395e-05</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>3.755558282136917e-05</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>1.986643837881275e-06</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>1.140911626862362e-05</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>2.899988248827867e-05</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>1.62789237947436e-05</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>6.775162091798848e-06</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>1.743659959174693e-05</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>3.267017018515617e-05</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>4.102702951058745e-05</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>4.007309325970709e-05</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>4.721219738712534e-05</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>4.862611240241677e-05</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>6.817911344114691e-05</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>2.747707912931219e-05</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>4.716587864095345e-05</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>4.893737786915153e-05</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>2.409339685982559e-05</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.0001116581843234599</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>1.008548451864044e-06</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>6.7401364503894e-05</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>3.361576091265306e-05</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>6.965905777178705e-05</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>1.932503073476255e-05</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>2.0131274141022e-05</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>1.615869223314803e-05</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>2.069177753583062e-05</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.0001290930085815489</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>7.44444114388898e-05</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>9.857016993919387e-05</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>4.490958963287994e-05</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.0001205470762215555</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>1.38623763632495e-05</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>7.851590635254979e-05</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>6.700785888824612e-05</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>1.580220487085171e-05</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>3.913992986781523e-05</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.0001950183359440416</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>3.248353459639475e-05</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.0001110694793169387</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>1.0976964404108e-05</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>3.012898014276288e-05</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>2.379688339715358e-05</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>1.347186116618104e-05</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>1.862807766883634e-05</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>6.941500760149211e-05</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>6.398886034730822e-05</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>1.255087590834592e-05</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.0001825021317927167</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>8.525674638804048e-05</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>2.506627606635448e-05</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>3.56614327756688e-05</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>2.736289025051519e-05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9.684785027275211e-07</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5.619906914944295e-06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.913781594950706e-07</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.713130131975049e-06</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.78321499536105e-06</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.052302291616797e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.796407898131292e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.58515966986306e-06</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.080403298052261e-07</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.367971880332334e-07</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.849195415270515e-06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.680597390281036e-06</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.080195594724501e-06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.673756161035271e-06</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.065810465661343e-05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.781623495844542e-06</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.687071966851363e-06</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2646103186853e-07</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.97168361637523e-08</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.724053042082232e-07</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.110426183004165e-06</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.557239657922764e-07</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9.018548894346168e-07</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.340832113783108e-06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.903189154807478e-07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.789565314742504e-06</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.29408384358976e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.666501248109853e-06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.679826482359204e-07</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.801201676698838e-07</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.139785920007853e-06</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.874179702099354e-06</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.961207090062089e-06</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.803770027843711e-07</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4.753524990519509e-06</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.498428218837944e-06</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>7.092679084053088e-07</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.90117475540319e-07</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.454897073926986e-07</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>3.587396406601329e-07</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.036801222653594e-06</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6.078618071114761e-07</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.119687110280211e-07</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.395747287664562e-06</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.810362727563188e-07</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.187052134810074e-06</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.045618986012414e-06</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.731909358379198e-07</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>9.906088962452486e-07</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.979099801654229e-06</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6.843269147793762e-06</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.955153372065979e-07</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.002920837185229e-06</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.427679863918456e-07</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.186841119415476e-07</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.137914978244225e-06</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.311314008489717e-06</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.303259634572896e-06</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.731100155666354e-06</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1.686076274154402e-07</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>7.477868848582148e-07</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>4.259712113707792e-06</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.206711423648812e-08</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>7.330048390485899e-08</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.32239881370333e-06</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>7.285259471245809e-07</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.977221018023556e-06</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.441351173525618e-06</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>8.206473012251081e-07</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1.970964149222709e-06</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.100851250157575e-06</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1.889286750156316e-06</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>2.328087873593176e-07</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>3.262189466113341e-06</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>7.506096153520048e-07</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1.223093363478256e-06</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.550179490550363e-06</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>3.292037717983476e-06</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>5.93773108903406e-07</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>1.619275508346618e-06</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>3.921083191471553e-08</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>6.817296593908395e-08</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>1.539155846330686e-06</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>3.818142886302667e-07</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>9.637009270591079e-07</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>8.825053328109789e-07</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>2.222833472842467e-06</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>6.137962600405444e-07</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>3.518284188430698e-07</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>8.774790671850496e-07</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>5.230546662460256e-08</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>3.010694854310714e-06</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>2.52499125963368e-06</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>4.111414909857558e-06</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>7.907331109890947e-07</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.965241608559154e-06</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>5.525971573661081e-07</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>1.867475816652586e-06</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>4.395261328227207e-07</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>2.268551355655291e-07</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.296880554946256e-06</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>4.113815634809725e-07</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>1.352280833089026e-06</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>9.975418606700259e-07</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>2.628138872751151e-06</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>1.381135206202089e-09</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>2.94321893079541e-07</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>5.485295559992664e-07</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>3.065380838052079e-07</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>2.980675617436646e-06</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>1.428810946890735e-06</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>9.656830002313654e-08</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>1.950915248016827e-06</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>2.240873754999484e-06</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>8.315998911712086e-07</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>4.079189466210664e-07</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>8.594325890953769e-07</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>4.153641555149079e-07</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2.482081811194803e-07</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>5.82933012083231e-07</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>5.600585382126155e-07</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>3.761632569876383e-07</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>1.434299576885678e-07</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>1.502299028288689e-06</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>2.710315811782493e-06</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>4.086997762442479e-07</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>4.012409817732987e-07</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>5.699266125702707e-07</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>7.213426442831405e-07</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>2.286475819346379e-06</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>1.259161081179627e-06</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>1.215090833284194e-06</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>6.004449915053556e-08</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>1.30082480609417e-06</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>2.496816705388483e-06</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>1.703787262385958e-07</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>7.792694418640167e-07</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>7.194722684289445e-07</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>5.608408741863968e-07</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>9.080452514353965e-07</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>1.606322939551319e-06</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>5.279367201183049e-07</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>3.415898675029894e-07</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>1.324608405184335e-07</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>4.805992261935899e-07</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>2.043582526312093e-06</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>1.157423412223579e-06</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>6.484280561380729e-07</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>2.65766459506267e-07</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>1.72747377291671e-06</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>9.894220056594349e-07</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>3.351842678966932e-07</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>6.103690566305886e-07</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>2.63361073393753e-07</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>2.125008450093446e-06</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>1.711809005655596e-07</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>1.616353529243497e-06</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>7.178064151958097e-07</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>2.286097696924116e-06</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>5.653748758049915e-07</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>1.38033925622949e-07</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>1.819516910472885e-07</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>1.619992673340676e-07</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>1.995362936213496e-06</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>1.335662318524555e-06</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>1.018633497551491e-06</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>2.397688149358146e-06</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>2.278970214319997e-06</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>1.277662249776768e-06</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>1.766970285643765e-06</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>2.901727384596597e-06</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>5.705722969651106e-07</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>5.009051733395609e-07</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>2.896080559366965e-06</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>1.40922225000395e-06</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>3.967805696447613e-06</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>6.030808208379312e-08</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>1.474039947879646e-07</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>4.079403879586607e-06</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>1.870885739663208e-07</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>6.232333475963969e-07</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>1.641509925320861e-06</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>2.432717565170606e-06</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>6.315553946478758e-08</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>3.058127049371251e-06</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>2.686270363483345e-06</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>2.506860141693323e-07</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>6.981475735301501e-07</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>7.436117925863073e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.0002845706476364285</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4.116450145374984e-05</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0003513158881105483</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.370500391814858e-06</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0002429278974886984</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0001889189588837326</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0001904700766317546</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.807941387407482e-05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.51759876543656e-05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0002218269655713812</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001012149587040767</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.000335507036652416</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.957719647791237e-05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0002134509268216789</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0003517789882607758</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0001557462674099952</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.422069029416889e-05</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.483511242549866e-05</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9.546357614453882e-05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.0002309273986611515</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.0001406455994583666</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.0001050041464623064</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.0001612154010217637</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.0001811901020118967</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.176505848998204e-05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.815273910528049e-05</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.70626405836083e-05</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.058411989011802e-05</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>9.519295417703688e-05</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.093514922307804e-06</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.054516466567293e-06</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5.25549694430083e-07</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.096018892596476e-05</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>8.404911932302639e-05</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.126984327333048e-05</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>4.749907020595856e-05</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.497523044236004e-05</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.0001532843452878296</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>6.919736188137904e-05</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6.246727571124211e-05</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>5.806615081382915e-05</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.330707502551377e-05</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.192896009655669e-05</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.161129956832156e-05</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.475112655200064e-05</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.136469083779957e-05</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.331449261168018e-05</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.0001664221053943038</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.248120527947322e-05</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.020934572210535e-05</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.0001953776954906061</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.746536407968961e-05</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.0001765969209372997</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.356993981171399e-05</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.0002097870601573959</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.369628292508423e-05</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.100907972315326e-06</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.306440728716552e-05</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>6.98645890224725e-05</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.912991663441062e-05</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>7.871654815971851e-05</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.000183473268407397</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.36747785290936e-05</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.0001067290431819856</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>8.782050281297415e-05</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.0001613433560123667</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.0001256528194062412</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.0001683606387814507</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.770026574376971e-05</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1.418005194864236e-05</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>5.979699926683679e-05</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>2.733158544288017e-05</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.774874494411051e-05</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.000199053916730918</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.0001503590756328776</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>7.558496145065874e-05</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.0001156370781245641</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.000233451573876664</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>7.526332410634495e-06</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>2.223123556177597e-05</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>3.954645217163488e-05</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>6.48438508505933e-05</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.0001357399742119014</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>7.506688416469842e-05</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>8.179075666703284e-05</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>5.263241473585367e-05</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>5.190487354411744e-05</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>4.671094757213723e-06</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>3.474405821179971e-05</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>2.136584225809202e-05</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.517998109397013e-05</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>6.703023245790973e-05</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>7.228417962323874e-05</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>4.121501842746511e-05</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>6.838799163233489e-05</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>3.489452501526102e-05</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.0001264276797883213</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>4.855604493059218e-05</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.282876110053621e-05</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>6.743473204551265e-05</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>9.504622721578926e-05</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>6.342241249512881e-05</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>7.703118171775714e-05</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>4.523683310253546e-05</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>5.475396028487012e-05</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>2.578637941041961e-05</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>1.031508782034507e-05</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>9.382628377352376e-06</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>8.372783486265689e-05</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>2.029938332270831e-05</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>8.753647853154689e-05</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>9.287933062296361e-05</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.0001209652400575578</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>6.690370355499908e-05</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>3.196422039764002e-05</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>3.395717430976219e-05</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>1.992621764657088e-05</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>3.052259125979617e-05</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>5.519985643331893e-05</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.0001550452725496143</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.0001169196766568348</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>4.054810415254906e-05</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.0001163043634733185</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>4.192177584627643e-05</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>7.888139407441486e-06</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>7.391051894956036e-06</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>4.963086030329578e-05</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>4.447580795385875e-05</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.0002256112347822636</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.0001201660998049192</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>2.728130129980855e-05</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.0001241442805621773</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>2.072961251542438e-05</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>2.55653740168782e-05</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>1.925789547385648e-06</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>3.364745498402044e-05</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.0001899069757200778</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>1.849455293267965e-05</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>5.304724982124753e-05</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.0001031080755637959</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>6.546754775627051e-06</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>2.999361277034041e-05</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>4.254993109498173e-05</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>3.496760837151669e-05</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>4.722438825410791e-05</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.0001221645652549341</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>6.350100011331961e-05</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>1.293811146751978e-05</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>3.061180905206129e-05</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.0001446355890948325</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>4.393735434859991e-05</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.0001642536517465487</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>4.494047607295215e-05</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>5.405039701145142e-05</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>9.381685958942398e-05</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>5.841600795974955e-05</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>9.20398160815239e-05</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>6.559869507327676e-05</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>8.444026752840728e-05</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>1.181417610496283e-05</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>4.956786142429337e-06</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>3.482586180325598e-06</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.0001010437117656693</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>5.009950837120414e-05</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>3.099008608842269e-05</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>6.718456279486418e-05</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.000169078863109462</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.0001702331937849522</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>5.207703361520544e-05</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.000123813355457969</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>5.254218922345899e-05</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>3.392765938770026e-05</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.0002019608800765127</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.0002510814229026437</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>2.407183637842536e-05</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.0003400120476726443</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>5.441458051791415e-05</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.0002336479956284165</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>8.208354120142758e-05</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.00012780494580511</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>3.680904046632349e-05</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>5.894929927308112e-05</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.0001227341126650572</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>4.456578244571574e-05</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>3.791035123867914e-05</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>5.053302811575122e-05</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>4.514684769674204e-05</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.0002294382429681718</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>6.806275632698089e-05</v>
       </c>
     </row>
   </sheetData>
